--- a/Documentacion/UVL_Desglose_Producción_Layout_V001.xlsx
+++ b/Documentacion/UVL_Desglose_Producción_Layout_V001.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Estudiante\Documents\Maye\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Documents\GitHub\Animacion3D_Cortometraje_NoEraSoloUnBoton\Documentacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23557784-34AF-48FD-AA4A-60D6E40D04DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12330"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Desglose_Producción" sheetId="1" r:id="rId1"/>
@@ -18,8 +19,17 @@
     <sheet name="Cronograma" sheetId="4" r:id="rId4"/>
     <sheet name="Presupuesto" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataChecksum="YGo6dJ0OLmfEmGjlCYFIrgIpVBI1Su0LvAesC3ef53o="/>
     </ext>
@@ -28,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="925" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="925" uniqueCount="250">
   <si>
     <t>NOMBRE LAYER</t>
   </si>
@@ -802,11 +812,14 @@
   <si>
     <t>Plano 11</t>
   </si>
+  <si>
+    <t>Personaje_01_Niño</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0"/>
   </numFmts>
@@ -2160,7 +2173,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2170,28 +2183,37 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="11" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2203,28 +2225,19 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="11" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2464,50 +2477,50 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I933"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.3984375" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" customWidth="1"/>
+    <col min="2" max="2" width="13.1328125" customWidth="1"/>
     <col min="3" max="3" width="32" customWidth="1"/>
-    <col min="4" max="4" width="11.28515625" customWidth="1"/>
-    <col min="5" max="5" width="33.140625" customWidth="1"/>
-    <col min="6" max="6" width="18.85546875" customWidth="1"/>
-    <col min="7" max="7" width="13.140625" customWidth="1"/>
-    <col min="8" max="8" width="31.7109375" customWidth="1"/>
-    <col min="9" max="9" width="16.7109375" customWidth="1"/>
-    <col min="10" max="26" width="10.7109375" customWidth="1"/>
+    <col min="4" max="4" width="11.265625" customWidth="1"/>
+    <col min="5" max="5" width="33.1328125" customWidth="1"/>
+    <col min="6" max="6" width="18.86328125" customWidth="1"/>
+    <col min="7" max="7" width="13.1328125" customWidth="1"/>
+    <col min="8" max="8" width="31.73046875" customWidth="1"/>
+    <col min="9" max="9" width="16.73046875" customWidth="1"/>
+    <col min="10" max="26" width="10.73046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.75">
-      <c r="A1" s="153" t="s">
+    <row r="1" spans="1:9" ht="15.4">
+      <c r="A1" s="160" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="154"/>
-      <c r="C1" s="154"/>
-      <c r="D1" s="154"/>
-      <c r="E1" s="154"/>
-      <c r="F1" s="154"/>
-      <c r="G1" s="154"/>
-      <c r="H1" s="154"/>
-      <c r="I1" s="155"/>
+      <c r="B1" s="161"/>
+      <c r="C1" s="161"/>
+      <c r="D1" s="161"/>
+      <c r="E1" s="161"/>
+      <c r="F1" s="161"/>
+      <c r="G1" s="161"/>
+      <c r="H1" s="161"/>
+      <c r="I1" s="162"/>
     </row>
     <row r="2" spans="1:9" ht="3" customHeight="1">
-      <c r="A2" s="156"/>
-      <c r="B2" s="157"/>
-      <c r="C2" s="157"/>
-      <c r="D2" s="157"/>
-      <c r="E2" s="157"/>
-      <c r="F2" s="157"/>
-      <c r="G2" s="157"/>
-      <c r="H2" s="157"/>
-      <c r="I2" s="158"/>
-    </row>
-    <row r="3" spans="1:9" ht="25.5">
+      <c r="A2" s="163"/>
+      <c r="B2" s="164"/>
+      <c r="C2" s="164"/>
+      <c r="D2" s="164"/>
+      <c r="E2" s="164"/>
+      <c r="F2" s="164"/>
+      <c r="G2" s="164"/>
+      <c r="H2" s="164"/>
+      <c r="I2" s="165"/>
+    </row>
+    <row r="3" spans="1:9" ht="26.25">
       <c r="A3" s="20" t="s">
         <v>4</v>
       </c>
@@ -2540,10 +2553,10 @@
       <c r="A4" s="142" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="144" t="s">
+      <c r="B4" s="139" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="144" t="s">
+      <c r="C4" s="139" t="s">
         <v>204</v>
       </c>
       <c r="D4" s="18">
@@ -2562,9 +2575,9 @@
       </c>
     </row>
     <row r="5" spans="1:9" ht="16.5" customHeight="1">
-      <c r="A5" s="151"/>
-      <c r="B5" s="152"/>
-      <c r="C5" s="152"/>
+      <c r="A5" s="149"/>
+      <c r="B5" s="154"/>
+      <c r="C5" s="154"/>
       <c r="D5" s="18">
         <v>3</v>
       </c>
@@ -2574,16 +2587,16 @@
       <c r="F5" s="21" t="s">
         <v>197</v>
       </c>
-      <c r="G5" s="149"/>
+      <c r="G5" s="155"/>
       <c r="H5" s="21"/>
       <c r="I5" s="29" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="16.5" customHeight="1">
-      <c r="A6" s="151"/>
-      <c r="B6" s="152"/>
-      <c r="C6" s="152"/>
+      <c r="A6" s="149"/>
+      <c r="B6" s="154"/>
+      <c r="C6" s="154"/>
       <c r="D6" s="18">
         <v>3</v>
       </c>
@@ -2593,7 +2606,7 @@
       <c r="F6" s="21" t="s">
         <v>198</v>
       </c>
-      <c r="G6" s="149"/>
+      <c r="G6" s="155"/>
       <c r="H6" s="21" t="s">
         <v>200</v>
       </c>
@@ -2602,9 +2615,9 @@
       </c>
     </row>
     <row r="7" spans="1:9" ht="16.5" customHeight="1">
-      <c r="A7" s="151"/>
-      <c r="B7" s="152"/>
-      <c r="C7" s="152"/>
+      <c r="A7" s="149"/>
+      <c r="B7" s="154"/>
+      <c r="C7" s="154"/>
       <c r="D7" s="18">
         <v>4</v>
       </c>
@@ -2614,7 +2627,7 @@
       <c r="F7" s="21" t="s">
         <v>199</v>
       </c>
-      <c r="G7" s="149"/>
+      <c r="G7" s="155"/>
       <c r="H7" s="21" t="s">
         <v>201</v>
       </c>
@@ -2633,7 +2646,7 @@
         <v>192</v>
       </c>
       <c r="F8" s="21" t="s">
-        <v>193</v>
+        <v>249</v>
       </c>
       <c r="G8" s="140"/>
       <c r="H8" s="21"/>
@@ -2641,25 +2654,25 @@
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
-      <c r="A9" s="148"/>
-      <c r="B9" s="146"/>
-      <c r="C9" s="146"/>
-      <c r="D9" s="146"/>
-      <c r="E9" s="146"/>
-      <c r="F9" s="146"/>
-      <c r="G9" s="146"/>
-      <c r="H9" s="146"/>
-      <c r="I9" s="147"/>
+    <row r="9" spans="1:9" ht="14.25">
+      <c r="A9" s="159"/>
+      <c r="B9" s="145"/>
+      <c r="C9" s="145"/>
+      <c r="D9" s="145"/>
+      <c r="E9" s="145"/>
+      <c r="F9" s="145"/>
+      <c r="G9" s="145"/>
+      <c r="H9" s="145"/>
+      <c r="I9" s="146"/>
     </row>
     <row r="10" spans="1:9" ht="18.75" customHeight="1">
       <c r="A10" s="142" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="144" t="s">
+      <c r="B10" s="139" t="s">
         <v>57</v>
       </c>
-      <c r="C10" s="144" t="s">
+      <c r="C10" s="139" t="s">
         <v>203</v>
       </c>
       <c r="D10" s="18">
@@ -2678,9 +2691,9 @@
       </c>
     </row>
     <row r="11" spans="1:9" ht="18.75" customHeight="1">
-      <c r="A11" s="151"/>
-      <c r="B11" s="152"/>
-      <c r="C11" s="152"/>
+      <c r="A11" s="149"/>
+      <c r="B11" s="154"/>
+      <c r="C11" s="154"/>
       <c r="D11" s="18">
         <v>2</v>
       </c>
@@ -2690,7 +2703,7 @@
       <c r="F11" s="21" t="s">
         <v>193</v>
       </c>
-      <c r="G11" s="149"/>
+      <c r="G11" s="155"/>
       <c r="H11" s="21" t="s">
         <v>202</v>
       </c>
@@ -2698,25 +2711,25 @@
         <v>51</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
-      <c r="A12" s="148"/>
-      <c r="B12" s="146"/>
-      <c r="C12" s="146"/>
-      <c r="D12" s="146"/>
-      <c r="E12" s="146"/>
-      <c r="F12" s="146"/>
-      <c r="G12" s="146"/>
-      <c r="H12" s="146"/>
-      <c r="I12" s="147"/>
+    <row r="12" spans="1:9" ht="14.25">
+      <c r="A12" s="159"/>
+      <c r="B12" s="145"/>
+      <c r="C12" s="145"/>
+      <c r="D12" s="145"/>
+      <c r="E12" s="145"/>
+      <c r="F12" s="145"/>
+      <c r="G12" s="145"/>
+      <c r="H12" s="145"/>
+      <c r="I12" s="146"/>
     </row>
     <row r="13" spans="1:9" ht="21" customHeight="1">
       <c r="A13" s="142" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="144" t="s">
+      <c r="B13" s="139" t="s">
         <v>67</v>
       </c>
-      <c r="C13" s="144" t="s">
+      <c r="C13" s="139" t="s">
         <v>205</v>
       </c>
       <c r="D13" s="18">
@@ -2728,7 +2741,7 @@
       <c r="F13" s="21" t="s">
         <v>198</v>
       </c>
-      <c r="G13" s="139"/>
+      <c r="G13" s="147"/>
       <c r="H13" s="21" t="s">
         <v>206</v>
       </c>
@@ -2737,9 +2750,9 @@
       </c>
     </row>
     <row r="14" spans="1:9" ht="21" customHeight="1">
-      <c r="A14" s="151"/>
-      <c r="B14" s="152"/>
-      <c r="C14" s="152"/>
+      <c r="A14" s="149"/>
+      <c r="B14" s="154"/>
+      <c r="C14" s="154"/>
       <c r="D14" s="18">
         <v>2</v>
       </c>
@@ -2749,22 +2762,22 @@
       <c r="F14" s="21" t="s">
         <v>199</v>
       </c>
-      <c r="G14" s="150"/>
+      <c r="G14" s="166"/>
       <c r="H14" s="21"/>
       <c r="I14" s="29" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A15" s="148"/>
-      <c r="B15" s="146"/>
-      <c r="C15" s="146"/>
-      <c r="D15" s="146"/>
-      <c r="E15" s="146"/>
-      <c r="F15" s="146"/>
-      <c r="G15" s="146"/>
-      <c r="H15" s="146"/>
-      <c r="I15" s="147"/>
+      <c r="A15" s="159"/>
+      <c r="B15" s="145"/>
+      <c r="C15" s="145"/>
+      <c r="D15" s="145"/>
+      <c r="E15" s="145"/>
+      <c r="F15" s="145"/>
+      <c r="G15" s="145"/>
+      <c r="H15" s="145"/>
+      <c r="I15" s="146"/>
     </row>
     <row r="16" spans="1:9" ht="28.5" customHeight="1">
       <c r="A16" s="63" t="s">
@@ -2799,10 +2812,10 @@
       <c r="A17" s="142" t="s">
         <v>91</v>
       </c>
-      <c r="B17" s="144" t="s">
+      <c r="B17" s="139" t="s">
         <v>72</v>
       </c>
-      <c r="C17" s="144" t="s">
+      <c r="C17" s="139" t="s">
         <v>207</v>
       </c>
       <c r="D17" s="18">
@@ -2814,7 +2827,7 @@
       <c r="F17" s="21" t="s">
         <v>209</v>
       </c>
-      <c r="G17" s="139"/>
+      <c r="G17" s="147"/>
       <c r="H17" s="21" t="s">
         <v>214</v>
       </c>
@@ -2861,24 +2874,24 @@
       </c>
     </row>
     <row r="20" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A20" s="145"/>
-      <c r="B20" s="146"/>
-      <c r="C20" s="146"/>
-      <c r="D20" s="146"/>
-      <c r="E20" s="146"/>
-      <c r="F20" s="146"/>
-      <c r="G20" s="146"/>
-      <c r="H20" s="146"/>
-      <c r="I20" s="147"/>
+      <c r="A20" s="144"/>
+      <c r="B20" s="145"/>
+      <c r="C20" s="145"/>
+      <c r="D20" s="145"/>
+      <c r="E20" s="145"/>
+      <c r="F20" s="145"/>
+      <c r="G20" s="145"/>
+      <c r="H20" s="145"/>
+      <c r="I20" s="146"/>
     </row>
     <row r="21" spans="1:9" ht="15.75" customHeight="1">
       <c r="A21" s="142" t="s">
         <v>91</v>
       </c>
-      <c r="B21" s="144" t="s">
+      <c r="B21" s="139" t="s">
         <v>81</v>
       </c>
-      <c r="C21" s="144" t="s">
+      <c r="C21" s="139" t="s">
         <v>215</v>
       </c>
       <c r="D21" s="18">
@@ -2890,7 +2903,7 @@
       <c r="F21" s="21" t="s">
         <v>219</v>
       </c>
-      <c r="G21" s="139"/>
+      <c r="G21" s="147"/>
       <c r="H21" s="21"/>
       <c r="I21" s="29" t="s">
         <v>51</v>
@@ -2916,24 +2929,24 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A23" s="145"/>
-      <c r="B23" s="146"/>
-      <c r="C23" s="146"/>
-      <c r="D23" s="146"/>
-      <c r="E23" s="146"/>
-      <c r="F23" s="146"/>
-      <c r="G23" s="146"/>
-      <c r="H23" s="146"/>
-      <c r="I23" s="147"/>
+      <c r="A23" s="144"/>
+      <c r="B23" s="145"/>
+      <c r="C23" s="145"/>
+      <c r="D23" s="145"/>
+      <c r="E23" s="145"/>
+      <c r="F23" s="145"/>
+      <c r="G23" s="145"/>
+      <c r="H23" s="145"/>
+      <c r="I23" s="146"/>
     </row>
     <row r="24" spans="1:9" ht="15.75" customHeight="1">
       <c r="A24" s="142" t="s">
         <v>91</v>
       </c>
-      <c r="B24" s="144" t="s">
+      <c r="B24" s="139" t="s">
         <v>85</v>
       </c>
-      <c r="C24" s="144" t="s">
+      <c r="C24" s="139" t="s">
         <v>216</v>
       </c>
       <c r="D24" s="18">
@@ -2945,7 +2958,7 @@
       <c r="F24" s="21" t="s">
         <v>209</v>
       </c>
-      <c r="G24" s="139"/>
+      <c r="G24" s="147"/>
       <c r="H24" s="21" t="s">
         <v>227</v>
       </c>
@@ -2975,24 +2988,24 @@
       </c>
     </row>
     <row r="26" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A26" s="145"/>
-      <c r="B26" s="146"/>
-      <c r="C26" s="146"/>
-      <c r="D26" s="146"/>
-      <c r="E26" s="146"/>
-      <c r="F26" s="146"/>
-      <c r="G26" s="146"/>
-      <c r="H26" s="146"/>
-      <c r="I26" s="147"/>
+      <c r="A26" s="144"/>
+      <c r="B26" s="145"/>
+      <c r="C26" s="145"/>
+      <c r="D26" s="145"/>
+      <c r="E26" s="145"/>
+      <c r="F26" s="145"/>
+      <c r="G26" s="145"/>
+      <c r="H26" s="145"/>
+      <c r="I26" s="146"/>
     </row>
     <row r="27" spans="1:9" ht="15.75" customHeight="1">
       <c r="A27" s="142" t="s">
         <v>91</v>
       </c>
-      <c r="B27" s="144" t="s">
+      <c r="B27" s="139" t="s">
         <v>222</v>
       </c>
-      <c r="C27" s="144" t="s">
+      <c r="C27" s="139" t="s">
         <v>215</v>
       </c>
       <c r="D27" s="18">
@@ -3062,10 +3075,10 @@
       <c r="A30" s="142" t="s">
         <v>109</v>
       </c>
-      <c r="B30" s="144" t="s">
+      <c r="B30" s="139" t="s">
         <v>223</v>
       </c>
-      <c r="C30" s="144" t="s">
+      <c r="C30" s="139" t="s">
         <v>224</v>
       </c>
       <c r="D30" s="18">
@@ -3242,10 +3255,10 @@
       <c r="A38" s="142" t="s">
         <v>115</v>
       </c>
-      <c r="B38" s="144" t="s">
+      <c r="B38" s="139" t="s">
         <v>237</v>
       </c>
-      <c r="C38" s="144" t="s">
+      <c r="C38" s="139" t="s">
         <v>238</v>
       </c>
       <c r="D38" s="18">
@@ -3302,24 +3315,24 @@
       </c>
     </row>
     <row r="41" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A41" s="162"/>
-      <c r="B41" s="146"/>
-      <c r="C41" s="146"/>
-      <c r="D41" s="146"/>
-      <c r="E41" s="146"/>
-      <c r="F41" s="146"/>
-      <c r="G41" s="146"/>
-      <c r="H41" s="146"/>
-      <c r="I41" s="147"/>
+      <c r="A41" s="148"/>
+      <c r="B41" s="145"/>
+      <c r="C41" s="145"/>
+      <c r="D41" s="145"/>
+      <c r="E41" s="145"/>
+      <c r="F41" s="145"/>
+      <c r="G41" s="145"/>
+      <c r="H41" s="145"/>
+      <c r="I41" s="146"/>
     </row>
     <row r="42" spans="1:9" ht="15.75" customHeight="1">
       <c r="A42" s="142" t="s">
         <v>115</v>
       </c>
-      <c r="B42" s="144" t="s">
+      <c r="B42" s="139" t="s">
         <v>245</v>
       </c>
-      <c r="C42" s="144" t="s">
+      <c r="C42" s="139" t="s">
         <v>246</v>
       </c>
       <c r="D42" s="18">
@@ -3338,9 +3351,9 @@
       </c>
     </row>
     <row r="43" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A43" s="151"/>
-      <c r="B43" s="152"/>
-      <c r="C43" s="152"/>
+      <c r="A43" s="149"/>
+      <c r="B43" s="154"/>
+      <c r="C43" s="154"/>
       <c r="D43" s="18">
         <v>2</v>
       </c>
@@ -3350,31 +3363,31 @@
       <c r="F43" s="21" t="s">
         <v>235</v>
       </c>
-      <c r="G43" s="149"/>
+      <c r="G43" s="155"/>
       <c r="H43" s="21"/>
       <c r="I43" s="29" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A44" s="162"/>
-      <c r="B44" s="146"/>
-      <c r="C44" s="146"/>
-      <c r="D44" s="146"/>
-      <c r="E44" s="146"/>
-      <c r="F44" s="146"/>
-      <c r="G44" s="146"/>
-      <c r="H44" s="146"/>
-      <c r="I44" s="147"/>
+      <c r="A44" s="148"/>
+      <c r="B44" s="145"/>
+      <c r="C44" s="145"/>
+      <c r="D44" s="145"/>
+      <c r="E44" s="145"/>
+      <c r="F44" s="145"/>
+      <c r="G44" s="145"/>
+      <c r="H44" s="145"/>
+      <c r="I44" s="146"/>
     </row>
     <row r="45" spans="1:9" ht="15.75" customHeight="1">
       <c r="A45" s="142" t="s">
         <v>115</v>
       </c>
-      <c r="B45" s="144" t="s">
+      <c r="B45" s="139" t="s">
         <v>248</v>
       </c>
-      <c r="C45" s="144" t="s">
+      <c r="C45" s="139" t="s">
         <v>125</v>
       </c>
       <c r="D45" s="18">
@@ -3496,9 +3509,9 @@
       </c>
     </row>
     <row r="51" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A51" s="161"/>
-      <c r="B51" s="160"/>
-      <c r="C51" s="160"/>
+      <c r="A51" s="157"/>
+      <c r="B51" s="150"/>
+      <c r="C51" s="150"/>
       <c r="D51" s="18">
         <v>7</v>
       </c>
@@ -3508,7 +3521,7 @@
       <c r="F51" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="G51" s="160"/>
+      <c r="G51" s="150"/>
       <c r="H51" s="21" t="s">
         <v>38</v>
       </c>
@@ -3549,10 +3562,10 @@
       <c r="A53" s="142" t="s">
         <v>131</v>
       </c>
-      <c r="B53" s="144" t="s">
+      <c r="B53" s="139" t="s">
         <v>21</v>
       </c>
-      <c r="C53" s="144" t="s">
+      <c r="C53" s="139" t="s">
         <v>132</v>
       </c>
       <c r="D53" s="18">
@@ -3568,7 +3581,7 @@
         <v>719</v>
       </c>
       <c r="H53" s="36"/>
-      <c r="I53" s="164" t="s">
+      <c r="I53" s="151" t="s">
         <v>152</v>
       </c>
     </row>
@@ -3589,7 +3602,7 @@
       <c r="H54" s="36" t="s">
         <v>154</v>
       </c>
-      <c r="I54" s="165"/>
+      <c r="I54" s="152"/>
     </row>
     <row r="55" spans="1:9" ht="15.75" customHeight="1">
       <c r="A55" s="143"/>
@@ -3608,12 +3621,12 @@
       <c r="H55" s="36" t="s">
         <v>154</v>
       </c>
-      <c r="I55" s="165"/>
+      <c r="I55" s="152"/>
     </row>
     <row r="56" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A56" s="161"/>
-      <c r="B56" s="160"/>
-      <c r="C56" s="160"/>
+      <c r="A56" s="157"/>
+      <c r="B56" s="150"/>
+      <c r="C56" s="150"/>
       <c r="D56" s="18">
         <v>4</v>
       </c>
@@ -3623,11 +3636,11 @@
       <c r="F56" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="G56" s="160"/>
+      <c r="G56" s="150"/>
       <c r="H56" s="36" t="s">
         <v>154</v>
       </c>
-      <c r="I56" s="166"/>
+      <c r="I56" s="153"/>
     </row>
     <row r="57" spans="1:9" ht="15.75" customHeight="1">
       <c r="A57" s="86" t="s">
@@ -3662,10 +3675,10 @@
       <c r="A58" s="142" t="s">
         <v>143</v>
       </c>
-      <c r="B58" s="144" t="s">
+      <c r="B58" s="139" t="s">
         <v>21</v>
       </c>
-      <c r="C58" s="144" t="s">
+      <c r="C58" s="139" t="s">
         <v>145</v>
       </c>
       <c r="D58" s="18">
@@ -3848,9 +3861,9 @@
       </c>
     </row>
     <row r="67" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A67" s="161"/>
-      <c r="B67" s="160"/>
-      <c r="C67" s="160"/>
+      <c r="A67" s="157"/>
+      <c r="B67" s="150"/>
+      <c r="C67" s="150"/>
       <c r="D67" s="18">
         <v>10</v>
       </c>
@@ -3860,7 +3873,7 @@
       <c r="F67" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="G67" s="160"/>
+      <c r="G67" s="150"/>
       <c r="H67" s="21" t="s">
         <v>38</v>
       </c>
@@ -3901,10 +3914,10 @@
       <c r="A69" s="142" t="s">
         <v>150</v>
       </c>
-      <c r="B69" s="144" t="s">
+      <c r="B69" s="139" t="s">
         <v>21</v>
       </c>
-      <c r="C69" s="144" t="s">
+      <c r="C69" s="139" t="s">
         <v>151</v>
       </c>
       <c r="D69" s="18">
@@ -4047,9 +4060,9 @@
       </c>
     </row>
     <row r="76" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A76" s="161"/>
-      <c r="B76" s="160"/>
-      <c r="C76" s="160"/>
+      <c r="A76" s="157"/>
+      <c r="B76" s="150"/>
+      <c r="C76" s="150"/>
       <c r="D76" s="18">
         <v>8</v>
       </c>
@@ -4059,7 +4072,7 @@
       <c r="F76" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="G76" s="160"/>
+      <c r="G76" s="150"/>
       <c r="H76" s="36"/>
       <c r="I76" s="29" t="s">
         <v>51</v>
@@ -4098,10 +4111,10 @@
       <c r="A78" s="142" t="s">
         <v>157</v>
       </c>
-      <c r="B78" s="144" t="s">
+      <c r="B78" s="139" t="s">
         <v>21</v>
       </c>
-      <c r="C78" s="144" t="s">
+      <c r="C78" s="139" t="s">
         <v>158</v>
       </c>
       <c r="D78" s="18">
@@ -4181,9 +4194,9 @@
       </c>
     </row>
     <row r="82" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A82" s="161"/>
-      <c r="B82" s="160"/>
-      <c r="C82" s="160"/>
+      <c r="A82" s="157"/>
+      <c r="B82" s="150"/>
+      <c r="C82" s="150"/>
       <c r="D82" s="18">
         <v>5</v>
       </c>
@@ -4193,7 +4206,7 @@
       <c r="F82" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="G82" s="160"/>
+      <c r="G82" s="150"/>
       <c r="H82" s="27"/>
       <c r="I82" s="29" t="s">
         <v>51</v>
@@ -4214,10 +4227,10 @@
       <c r="A84" s="142" t="s">
         <v>157</v>
       </c>
-      <c r="B84" s="144" t="s">
+      <c r="B84" s="139" t="s">
         <v>57</v>
       </c>
-      <c r="C84" s="144" t="s">
+      <c r="C84" s="139" t="s">
         <v>161</v>
       </c>
       <c r="D84" s="18">
@@ -4320,9 +4333,9 @@
       </c>
     </row>
     <row r="89" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A89" s="163"/>
-      <c r="B89" s="159"/>
-      <c r="C89" s="159"/>
+      <c r="A89" s="158"/>
+      <c r="B89" s="156"/>
+      <c r="C89" s="156"/>
       <c r="D89" s="108">
         <v>6</v>
       </c>
@@ -4332,7 +4345,7 @@
       <c r="F89" s="109" t="s">
         <v>31</v>
       </c>
-      <c r="G89" s="159"/>
+      <c r="G89" s="156"/>
       <c r="H89" s="110"/>
       <c r="I89" s="111" t="s">
         <v>51</v>
@@ -6872,25 +6885,41 @@
     </row>
   </sheetData>
   <mergeCells count="75">
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="G27:G28"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="C21:C22"/>
-    <mergeCell ref="A23:I23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="G24:G25"/>
-    <mergeCell ref="A41:I41"/>
-    <mergeCell ref="A42:A43"/>
-    <mergeCell ref="G53:G56"/>
-    <mergeCell ref="I53:I56"/>
-    <mergeCell ref="G58:G67"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="C42:C43"/>
-    <mergeCell ref="G42:G43"/>
+    <mergeCell ref="G38:G40"/>
+    <mergeCell ref="A17:A19"/>
+    <mergeCell ref="B17:B19"/>
+    <mergeCell ref="C17:C19"/>
+    <mergeCell ref="A20:I20"/>
+    <mergeCell ref="A30:A36"/>
+    <mergeCell ref="G30:G36"/>
+    <mergeCell ref="B30:B36"/>
+    <mergeCell ref="C30:C36"/>
+    <mergeCell ref="A38:A40"/>
+    <mergeCell ref="B38:B40"/>
+    <mergeCell ref="C38:C40"/>
+    <mergeCell ref="A26:I26"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="A12:I12"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="G17:G19"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="B69:B76"/>
+    <mergeCell ref="C69:C76"/>
+    <mergeCell ref="A15:I15"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A4:A8"/>
+    <mergeCell ref="B4:B8"/>
+    <mergeCell ref="C4:C8"/>
+    <mergeCell ref="G4:G8"/>
+    <mergeCell ref="A9:I9"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
     <mergeCell ref="G69:G76"/>
     <mergeCell ref="G78:G82"/>
     <mergeCell ref="G84:G89"/>
@@ -6907,46 +6936,30 @@
     <mergeCell ref="A84:A89"/>
     <mergeCell ref="B84:B89"/>
     <mergeCell ref="C84:C89"/>
+    <mergeCell ref="A41:I41"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="G53:G56"/>
+    <mergeCell ref="I53:I56"/>
+    <mergeCell ref="G58:G67"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="C42:C43"/>
+    <mergeCell ref="G42:G43"/>
     <mergeCell ref="B53:B56"/>
     <mergeCell ref="C53:C56"/>
     <mergeCell ref="A58:A67"/>
     <mergeCell ref="B58:B67"/>
     <mergeCell ref="C58:C67"/>
-    <mergeCell ref="B69:B76"/>
-    <mergeCell ref="C69:C76"/>
-    <mergeCell ref="A15:I15"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A4:A8"/>
-    <mergeCell ref="B4:B8"/>
-    <mergeCell ref="C4:C8"/>
-    <mergeCell ref="G4:G8"/>
-    <mergeCell ref="A9:I9"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="G13:G14"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="A12:I12"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="G17:G19"/>
-    <mergeCell ref="G21:G22"/>
-    <mergeCell ref="G38:G40"/>
-    <mergeCell ref="A17:A19"/>
-    <mergeCell ref="B17:B19"/>
-    <mergeCell ref="C17:C19"/>
-    <mergeCell ref="A20:I20"/>
-    <mergeCell ref="A30:A36"/>
-    <mergeCell ref="G30:G36"/>
-    <mergeCell ref="B30:B36"/>
-    <mergeCell ref="C30:C36"/>
-    <mergeCell ref="A38:A40"/>
-    <mergeCell ref="B38:B40"/>
-    <mergeCell ref="C38:C40"/>
-    <mergeCell ref="A26:I26"/>
-    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="G27:G28"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="A23:I23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="G24:G25"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.64" bottom="0.08" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -6954,24 +6967,24 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:I1000"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.3984375" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="24.85546875" customWidth="1"/>
-    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+    <col min="1" max="1" width="24.86328125" customWidth="1"/>
+    <col min="2" max="2" width="16.86328125" customWidth="1"/>
     <col min="3" max="3" width="10" customWidth="1"/>
-    <col min="4" max="4" width="12.7109375" customWidth="1"/>
-    <col min="5" max="5" width="11.140625" customWidth="1"/>
-    <col min="6" max="6" width="15.140625" customWidth="1"/>
-    <col min="7" max="7" width="13.85546875" customWidth="1"/>
-    <col min="8" max="8" width="10.5703125" customWidth="1"/>
-    <col min="9" max="9" width="13.85546875" customWidth="1"/>
-    <col min="10" max="10" width="4.42578125" customWidth="1"/>
-    <col min="11" max="26" width="10.7109375" customWidth="1"/>
+    <col min="4" max="4" width="12.73046875" customWidth="1"/>
+    <col min="5" max="5" width="11.1328125" customWidth="1"/>
+    <col min="6" max="6" width="15.1328125" customWidth="1"/>
+    <col min="7" max="7" width="13.86328125" customWidth="1"/>
+    <col min="8" max="8" width="10.59765625" customWidth="1"/>
+    <col min="9" max="9" width="13.86328125" customWidth="1"/>
+    <col min="10" max="10" width="4.3984375" customWidth="1"/>
+    <col min="11" max="26" width="10.73046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="25.5">
+    <row r="1" spans="1:9" ht="26.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7000,7 +7013,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" ht="14.25">
       <c r="A2" s="9" t="s">
         <v>16</v>
       </c>
@@ -7015,7 +7028,7 @@
       <c r="H2" s="15"/>
       <c r="I2" s="16"/>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" ht="14.25">
       <c r="A3" s="17" t="s">
         <v>23</v>
       </c>
@@ -7030,7 +7043,7 @@
       <c r="H3" s="25"/>
       <c r="I3" s="27"/>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" ht="14.25">
       <c r="A4" s="17" t="s">
         <v>30</v>
       </c>
@@ -7045,7 +7058,7 @@
       <c r="H4" s="25"/>
       <c r="I4" s="27"/>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" ht="14.25">
       <c r="A5" s="17" t="s">
         <v>34</v>
       </c>
@@ -7060,7 +7073,7 @@
       <c r="H5" s="25"/>
       <c r="I5" s="22"/>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" ht="14.25">
       <c r="A6" s="30" t="s">
         <v>40</v>
       </c>
@@ -7075,7 +7088,7 @@
       <c r="H6" s="25"/>
       <c r="I6" s="27"/>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" ht="14.25">
       <c r="A7" s="17" t="s">
         <v>45</v>
       </c>
@@ -7090,7 +7103,7 @@
       <c r="H7" s="25"/>
       <c r="I7" s="22"/>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" ht="14.25">
       <c r="A8" s="17" t="s">
         <v>52</v>
       </c>
@@ -7105,7 +7118,7 @@
       <c r="H8" s="25"/>
       <c r="I8" s="27"/>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" ht="14.25">
       <c r="A9" s="17" t="s">
         <v>56</v>
       </c>
@@ -7120,7 +7133,7 @@
       <c r="H9" s="25"/>
       <c r="I9" s="27"/>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" ht="14.25">
       <c r="A10" s="17" t="s">
         <v>60</v>
       </c>
@@ -7135,7 +7148,7 @@
       <c r="H10" s="25"/>
       <c r="I10" s="27"/>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" ht="14.25">
       <c r="A11" s="17" t="s">
         <v>62</v>
       </c>
@@ -7150,7 +7163,7 @@
       <c r="H11" s="25"/>
       <c r="I11" s="22"/>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:9" ht="14.25">
       <c r="A12" s="17" t="s">
         <v>62</v>
       </c>
@@ -7165,7 +7178,7 @@
       <c r="H12" s="25"/>
       <c r="I12" s="27"/>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:9" ht="14.25">
       <c r="A13" s="17" t="s">
         <v>25</v>
       </c>
@@ -7180,7 +7193,7 @@
       <c r="H13" s="25"/>
       <c r="I13" s="27"/>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:9" ht="14.25">
       <c r="A14" s="17" t="s">
         <v>32</v>
       </c>
@@ -7195,7 +7208,7 @@
       <c r="H14" s="25"/>
       <c r="I14" s="27"/>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:9" ht="14.25">
       <c r="A15" s="45" t="s">
         <v>46</v>
       </c>
@@ -8197,24 +8210,24 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:J1000"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.3984375" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" customWidth="1"/>
-    <col min="3" max="3" width="25.140625" customWidth="1"/>
-    <col min="4" max="4" width="11.28515625" customWidth="1"/>
+    <col min="2" max="2" width="13.1328125" customWidth="1"/>
+    <col min="3" max="3" width="25.1328125" customWidth="1"/>
+    <col min="4" max="4" width="11.265625" customWidth="1"/>
     <col min="5" max="5" width="26" customWidth="1"/>
-    <col min="6" max="6" width="18.85546875" customWidth="1"/>
-    <col min="7" max="7" width="13.140625" customWidth="1"/>
-    <col min="8" max="8" width="18.7109375" customWidth="1"/>
-    <col min="9" max="9" width="16.7109375" customWidth="1"/>
-    <col min="10" max="10" width="50.42578125" customWidth="1"/>
-    <col min="11" max="26" width="10.7109375" customWidth="1"/>
+    <col min="6" max="6" width="18.86328125" customWidth="1"/>
+    <col min="7" max="7" width="13.1328125" customWidth="1"/>
+    <col min="8" max="8" width="18.73046875" customWidth="1"/>
+    <col min="9" max="9" width="16.73046875" customWidth="1"/>
+    <col min="10" max="10" width="50.3984375" customWidth="1"/>
+    <col min="11" max="26" width="10.73046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="25.5">
+    <row r="1" spans="1:10" ht="26.25">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -8244,14 +8257,14 @@
       </c>
       <c r="J1" s="13"/>
     </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="144" t="s">
+    <row r="2" spans="1:10" ht="14.25">
+      <c r="A2" s="139" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="144" t="s">
+      <c r="B2" s="139" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="144" t="s">
+      <c r="C2" s="139" t="s">
         <v>22</v>
       </c>
       <c r="D2" s="18">
@@ -8272,7 +8285,7 @@
       <c r="I2" s="24"/>
       <c r="J2" s="13"/>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" ht="14.25">
       <c r="A3" s="140"/>
       <c r="B3" s="140"/>
       <c r="C3" s="140"/>
@@ -8292,7 +8305,7 @@
       <c r="I3" s="24"/>
       <c r="J3" s="13"/>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" ht="14.25">
       <c r="A4" s="140"/>
       <c r="B4" s="140"/>
       <c r="C4" s="140"/>
@@ -8312,7 +8325,7 @@
       <c r="I4" s="24"/>
       <c r="J4" s="13"/>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" ht="14.25">
       <c r="A5" s="140"/>
       <c r="B5" s="140"/>
       <c r="C5" s="140"/>
@@ -8332,10 +8345,10 @@
       <c r="I5" s="24"/>
       <c r="J5" s="13"/>
     </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="160"/>
-      <c r="B6" s="160"/>
-      <c r="C6" s="160"/>
+    <row r="6" spans="1:10" ht="14.25">
+      <c r="A6" s="150"/>
+      <c r="B6" s="150"/>
+      <c r="C6" s="150"/>
       <c r="D6" s="18">
         <v>6</v>
       </c>
@@ -8345,33 +8358,33 @@
       <c r="F6" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="G6" s="160"/>
+      <c r="G6" s="150"/>
       <c r="H6" s="21" t="s">
         <v>27</v>
       </c>
       <c r="I6" s="24"/>
       <c r="J6" s="13"/>
     </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="171"/>
-      <c r="B7" s="146"/>
-      <c r="C7" s="146"/>
-      <c r="D7" s="146"/>
-      <c r="E7" s="146"/>
-      <c r="F7" s="146"/>
-      <c r="G7" s="146"/>
-      <c r="H7" s="146"/>
+    <row r="7" spans="1:10" ht="14.25">
+      <c r="A7" s="172"/>
+      <c r="B7" s="145"/>
+      <c r="C7" s="145"/>
+      <c r="D7" s="145"/>
+      <c r="E7" s="145"/>
+      <c r="F7" s="145"/>
+      <c r="G7" s="145"/>
+      <c r="H7" s="145"/>
       <c r="I7" s="170"/>
       <c r="J7" s="13"/>
     </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="144" t="s">
+    <row r="8" spans="1:10" ht="14.25">
+      <c r="A8" s="139" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="144" t="s">
+      <c r="B8" s="139" t="s">
         <v>57</v>
       </c>
-      <c r="C8" s="144" t="s">
+      <c r="C8" s="139" t="s">
         <v>59</v>
       </c>
       <c r="D8" s="18">
@@ -8392,7 +8405,7 @@
       <c r="I8" s="24"/>
       <c r="J8" s="13"/>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" ht="14.25">
       <c r="A9" s="140"/>
       <c r="B9" s="140"/>
       <c r="C9" s="140"/>
@@ -8412,7 +8425,7 @@
       <c r="I9" s="24"/>
       <c r="J9" s="13"/>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" ht="14.25">
       <c r="A10" s="140"/>
       <c r="B10" s="140"/>
       <c r="C10" s="140"/>
@@ -8432,7 +8445,7 @@
       <c r="I10" s="24"/>
       <c r="J10" s="13"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" ht="14.25">
       <c r="A11" s="140"/>
       <c r="B11" s="140"/>
       <c r="C11" s="140"/>
@@ -8452,10 +8465,10 @@
       <c r="I11" s="24"/>
       <c r="J11" s="13"/>
     </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="160"/>
-      <c r="B12" s="160"/>
-      <c r="C12" s="160"/>
+    <row r="12" spans="1:10" ht="14.25">
+      <c r="A12" s="150"/>
+      <c r="B12" s="150"/>
+      <c r="C12" s="150"/>
       <c r="D12" s="18">
         <v>6</v>
       </c>
@@ -8465,33 +8478,33 @@
       <c r="F12" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="G12" s="160"/>
+      <c r="G12" s="150"/>
       <c r="H12" s="21" t="s">
         <v>27</v>
       </c>
       <c r="I12" s="24"/>
       <c r="J12" s="13"/>
     </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="171"/>
-      <c r="B13" s="146"/>
-      <c r="C13" s="146"/>
-      <c r="D13" s="146"/>
-      <c r="E13" s="146"/>
-      <c r="F13" s="146"/>
-      <c r="G13" s="146"/>
-      <c r="H13" s="146"/>
+    <row r="13" spans="1:10" ht="14.25">
+      <c r="A13" s="172"/>
+      <c r="B13" s="145"/>
+      <c r="C13" s="145"/>
+      <c r="D13" s="145"/>
+      <c r="E13" s="145"/>
+      <c r="F13" s="145"/>
+      <c r="G13" s="145"/>
+      <c r="H13" s="145"/>
       <c r="I13" s="170"/>
       <c r="J13" s="13"/>
     </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="144" t="s">
+    <row r="14" spans="1:10" ht="14.25">
+      <c r="A14" s="139" t="s">
         <v>20</v>
       </c>
-      <c r="B14" s="144" t="s">
+      <c r="B14" s="139" t="s">
         <v>67</v>
       </c>
-      <c r="C14" s="144" t="s">
+      <c r="C14" s="139" t="s">
         <v>68</v>
       </c>
       <c r="D14" s="18">
@@ -8503,7 +8516,7 @@
       <c r="F14" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="G14" s="139">
+      <c r="G14" s="147">
         <v>96</v>
       </c>
       <c r="H14" s="21" t="s">
@@ -8512,7 +8525,7 @@
       <c r="I14" s="24"/>
       <c r="J14" s="13"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" ht="14.25">
       <c r="A15" s="140"/>
       <c r="B15" s="140"/>
       <c r="C15" s="140"/>
@@ -8532,7 +8545,7 @@
       <c r="I15" s="24"/>
       <c r="J15" s="13"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" ht="14.25">
       <c r="A16" s="140"/>
       <c r="B16" s="140"/>
       <c r="C16" s="140"/>
@@ -8554,7 +8567,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" ht="14.25">
       <c r="A17" s="140"/>
       <c r="B17" s="140"/>
       <c r="C17" s="140"/>
@@ -8574,10 +8587,10 @@
       <c r="I17" s="24"/>
       <c r="J17" s="13"/>
     </row>
-    <row r="18" spans="1:10">
-      <c r="A18" s="160"/>
-      <c r="B18" s="160"/>
-      <c r="C18" s="160"/>
+    <row r="18" spans="1:10" ht="14.25">
+      <c r="A18" s="150"/>
+      <c r="B18" s="150"/>
+      <c r="C18" s="150"/>
       <c r="D18" s="18">
         <v>9</v>
       </c>
@@ -8587,33 +8600,33 @@
       <c r="F18" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="G18" s="160"/>
+      <c r="G18" s="150"/>
       <c r="H18" s="21" t="s">
         <v>27</v>
       </c>
       <c r="I18" s="24"/>
       <c r="J18" s="13"/>
     </row>
-    <row r="19" spans="1:10">
-      <c r="A19" s="171"/>
-      <c r="B19" s="146"/>
-      <c r="C19" s="146"/>
-      <c r="D19" s="146"/>
-      <c r="E19" s="146"/>
-      <c r="F19" s="146"/>
-      <c r="G19" s="146"/>
-      <c r="H19" s="146"/>
+    <row r="19" spans="1:10" ht="14.25">
+      <c r="A19" s="172"/>
+      <c r="B19" s="145"/>
+      <c r="C19" s="145"/>
+      <c r="D19" s="145"/>
+      <c r="E19" s="145"/>
+      <c r="F19" s="145"/>
+      <c r="G19" s="145"/>
+      <c r="H19" s="145"/>
       <c r="I19" s="170"/>
       <c r="J19" s="13"/>
     </row>
-    <row r="20" spans="1:10">
-      <c r="A20" s="144" t="s">
+    <row r="20" spans="1:10" ht="14.25">
+      <c r="A20" s="139" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="144" t="s">
+      <c r="B20" s="139" t="s">
         <v>72</v>
       </c>
-      <c r="C20" s="144" t="s">
+      <c r="C20" s="139" t="s">
         <v>74</v>
       </c>
       <c r="D20" s="18">
@@ -8625,7 +8638,7 @@
       <c r="F20" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="G20" s="139">
+      <c r="G20" s="147">
         <v>109</v>
       </c>
       <c r="H20" s="21" t="s">
@@ -8695,9 +8708,9 @@
       <c r="J23" s="13"/>
     </row>
     <row r="24" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A24" s="160"/>
-      <c r="B24" s="160"/>
-      <c r="C24" s="160"/>
+      <c r="A24" s="150"/>
+      <c r="B24" s="150"/>
+      <c r="C24" s="150"/>
       <c r="D24" s="18">
         <v>6</v>
       </c>
@@ -8707,7 +8720,7 @@
       <c r="F24" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="G24" s="160"/>
+      <c r="G24" s="150"/>
       <c r="H24" s="21" t="s">
         <v>27</v>
       </c>
@@ -8715,25 +8728,25 @@
       <c r="J24" s="13"/>
     </row>
     <row r="25" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A25" s="171"/>
-      <c r="B25" s="146"/>
-      <c r="C25" s="146"/>
-      <c r="D25" s="146"/>
-      <c r="E25" s="146"/>
-      <c r="F25" s="146"/>
-      <c r="G25" s="146"/>
-      <c r="H25" s="146"/>
+      <c r="A25" s="172"/>
+      <c r="B25" s="145"/>
+      <c r="C25" s="145"/>
+      <c r="D25" s="145"/>
+      <c r="E25" s="145"/>
+      <c r="F25" s="145"/>
+      <c r="G25" s="145"/>
+      <c r="H25" s="145"/>
       <c r="I25" s="170"/>
       <c r="J25" s="13"/>
     </row>
     <row r="26" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A26" s="144" t="s">
+      <c r="A26" s="139" t="s">
         <v>20</v>
       </c>
-      <c r="B26" s="144" t="s">
+      <c r="B26" s="139" t="s">
         <v>81</v>
       </c>
-      <c r="C26" s="144" t="s">
+      <c r="C26" s="139" t="s">
         <v>82</v>
       </c>
       <c r="D26" s="18">
@@ -8745,7 +8758,7 @@
       <c r="F26" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="G26" s="139">
+      <c r="G26" s="147">
         <v>95</v>
       </c>
       <c r="H26" s="21" t="s">
@@ -8815,9 +8828,9 @@
       <c r="J29" s="13"/>
     </row>
     <row r="30" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A30" s="160"/>
-      <c r="B30" s="160"/>
-      <c r="C30" s="160"/>
+      <c r="A30" s="150"/>
+      <c r="B30" s="150"/>
+      <c r="C30" s="150"/>
       <c r="D30" s="18">
         <v>6</v>
       </c>
@@ -8827,7 +8840,7 @@
       <c r="F30" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="G30" s="160"/>
+      <c r="G30" s="150"/>
       <c r="H30" s="21" t="s">
         <v>27</v>
       </c>
@@ -8835,25 +8848,25 @@
       <c r="J30" s="13"/>
     </row>
     <row r="31" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A31" s="171"/>
-      <c r="B31" s="146"/>
-      <c r="C31" s="146"/>
-      <c r="D31" s="146"/>
-      <c r="E31" s="146"/>
-      <c r="F31" s="146"/>
-      <c r="G31" s="146"/>
-      <c r="H31" s="146"/>
+      <c r="A31" s="172"/>
+      <c r="B31" s="145"/>
+      <c r="C31" s="145"/>
+      <c r="D31" s="145"/>
+      <c r="E31" s="145"/>
+      <c r="F31" s="145"/>
+      <c r="G31" s="145"/>
+      <c r="H31" s="145"/>
       <c r="I31" s="170"/>
       <c r="J31" s="13"/>
     </row>
     <row r="32" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A32" s="144" t="s">
+      <c r="A32" s="139" t="s">
         <v>20</v>
       </c>
-      <c r="B32" s="144" t="s">
+      <c r="B32" s="139" t="s">
         <v>85</v>
       </c>
-      <c r="C32" s="144" t="s">
+      <c r="C32" s="139" t="s">
         <v>86</v>
       </c>
       <c r="D32" s="18">
@@ -8865,7 +8878,7 @@
       <c r="F32" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="G32" s="139">
+      <c r="G32" s="147">
         <v>48</v>
       </c>
       <c r="H32" s="21" t="s">
@@ -8937,9 +8950,9 @@
       <c r="J35" s="13"/>
     </row>
     <row r="36" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A36" s="160"/>
-      <c r="B36" s="160"/>
-      <c r="C36" s="160"/>
+      <c r="A36" s="150"/>
+      <c r="B36" s="150"/>
+      <c r="C36" s="150"/>
       <c r="D36" s="18">
         <v>7</v>
       </c>
@@ -8949,7 +8962,7 @@
       <c r="F36" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="G36" s="160"/>
+      <c r="G36" s="150"/>
       <c r="H36" s="21" t="s">
         <v>27</v>
       </c>
@@ -8987,13 +9000,13 @@
       <c r="J37" s="13"/>
     </row>
     <row r="38" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A38" s="144" t="s">
+      <c r="A38" s="139" t="s">
         <v>91</v>
       </c>
-      <c r="B38" s="144" t="s">
+      <c r="B38" s="139" t="s">
         <v>21</v>
       </c>
-      <c r="C38" s="144" t="s">
+      <c r="C38" s="139" t="s">
         <v>93</v>
       </c>
       <c r="D38" s="18">
@@ -9005,7 +9018,7 @@
       <c r="F38" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="G38" s="139">
+      <c r="G38" s="147">
         <v>71</v>
       </c>
       <c r="H38" s="21" t="s">
@@ -9075,9 +9088,9 @@
       <c r="J41" s="13"/>
     </row>
     <row r="42" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A42" s="160"/>
-      <c r="B42" s="160"/>
-      <c r="C42" s="160"/>
+      <c r="A42" s="150"/>
+      <c r="B42" s="150"/>
+      <c r="C42" s="150"/>
       <c r="D42" s="18">
         <v>10</v>
       </c>
@@ -9087,7 +9100,7 @@
       <c r="F42" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="G42" s="160"/>
+      <c r="G42" s="150"/>
       <c r="H42" s="21" t="s">
         <v>27</v>
       </c>
@@ -9096,24 +9109,24 @@
     </row>
     <row r="43" spans="1:10" ht="15.75" customHeight="1">
       <c r="A43" s="169"/>
-      <c r="B43" s="146"/>
-      <c r="C43" s="146"/>
-      <c r="D43" s="146"/>
-      <c r="E43" s="146"/>
-      <c r="F43" s="146"/>
-      <c r="G43" s="146"/>
-      <c r="H43" s="146"/>
+      <c r="B43" s="145"/>
+      <c r="C43" s="145"/>
+      <c r="D43" s="145"/>
+      <c r="E43" s="145"/>
+      <c r="F43" s="145"/>
+      <c r="G43" s="145"/>
+      <c r="H43" s="145"/>
       <c r="I43" s="170"/>
       <c r="J43" s="13"/>
     </row>
     <row r="44" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A44" s="144" t="s">
+      <c r="A44" s="139" t="s">
         <v>91</v>
       </c>
-      <c r="B44" s="144" t="s">
+      <c r="B44" s="139" t="s">
         <v>57</v>
       </c>
-      <c r="C44" s="144" t="s">
+      <c r="C44" s="139" t="s">
         <v>97</v>
       </c>
       <c r="D44" s="18">
@@ -9125,7 +9138,7 @@
       <c r="F44" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="G44" s="139">
+      <c r="G44" s="147">
         <v>103</v>
       </c>
       <c r="H44" s="21" t="s">
@@ -9195,9 +9208,9 @@
       <c r="J47" s="13"/>
     </row>
     <row r="48" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A48" s="160"/>
-      <c r="B48" s="160"/>
-      <c r="C48" s="160"/>
+      <c r="A48" s="150"/>
+      <c r="B48" s="150"/>
+      <c r="C48" s="150"/>
       <c r="D48" s="18">
         <v>10</v>
       </c>
@@ -9207,7 +9220,7 @@
       <c r="F48" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="G48" s="160"/>
+      <c r="G48" s="150"/>
       <c r="H48" s="21" t="s">
         <v>27</v>
       </c>
@@ -9216,24 +9229,24 @@
     </row>
     <row r="49" spans="1:10" ht="15.75" customHeight="1">
       <c r="A49" s="169"/>
-      <c r="B49" s="146"/>
-      <c r="C49" s="146"/>
-      <c r="D49" s="146"/>
-      <c r="E49" s="146"/>
-      <c r="F49" s="146"/>
-      <c r="G49" s="146"/>
-      <c r="H49" s="146"/>
+      <c r="B49" s="145"/>
+      <c r="C49" s="145"/>
+      <c r="D49" s="145"/>
+      <c r="E49" s="145"/>
+      <c r="F49" s="145"/>
+      <c r="G49" s="145"/>
+      <c r="H49" s="145"/>
       <c r="I49" s="170"/>
       <c r="J49" s="13"/>
     </row>
     <row r="50" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A50" s="144" t="s">
+      <c r="A50" s="139" t="s">
         <v>91</v>
       </c>
-      <c r="B50" s="144" t="s">
+      <c r="B50" s="139" t="s">
         <v>67</v>
       </c>
-      <c r="C50" s="144" t="s">
+      <c r="C50" s="139" t="s">
         <v>101</v>
       </c>
       <c r="D50" s="18">
@@ -9245,7 +9258,7 @@
       <c r="F50" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="G50" s="139">
+      <c r="G50" s="147">
         <v>92</v>
       </c>
       <c r="H50" s="21" t="s">
@@ -9315,9 +9328,9 @@
       <c r="J53" s="13"/>
     </row>
     <row r="54" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A54" s="160"/>
-      <c r="B54" s="160"/>
-      <c r="C54" s="160"/>
+      <c r="A54" s="150"/>
+      <c r="B54" s="150"/>
+      <c r="C54" s="150"/>
       <c r="D54" s="18">
         <v>7</v>
       </c>
@@ -9327,7 +9340,7 @@
       <c r="F54" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="G54" s="160"/>
+      <c r="G54" s="150"/>
       <c r="H54" s="21" t="s">
         <v>27</v>
       </c>
@@ -9336,24 +9349,24 @@
     </row>
     <row r="55" spans="1:10" ht="15.75" customHeight="1">
       <c r="A55" s="169"/>
-      <c r="B55" s="146"/>
-      <c r="C55" s="146"/>
-      <c r="D55" s="146"/>
-      <c r="E55" s="146"/>
-      <c r="F55" s="146"/>
-      <c r="G55" s="146"/>
-      <c r="H55" s="146"/>
+      <c r="B55" s="145"/>
+      <c r="C55" s="145"/>
+      <c r="D55" s="145"/>
+      <c r="E55" s="145"/>
+      <c r="F55" s="145"/>
+      <c r="G55" s="145"/>
+      <c r="H55" s="145"/>
       <c r="I55" s="170"/>
       <c r="J55" s="13"/>
     </row>
     <row r="56" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A56" s="144" t="s">
+      <c r="A56" s="139" t="s">
         <v>91</v>
       </c>
-      <c r="B56" s="144" t="s">
+      <c r="B56" s="139" t="s">
         <v>72</v>
       </c>
-      <c r="C56" s="144" t="s">
+      <c r="C56" s="139" t="s">
         <v>105</v>
       </c>
       <c r="D56" s="18">
@@ -9435,9 +9448,9 @@
       <c r="J59" s="13"/>
     </row>
     <row r="60" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A60" s="160"/>
-      <c r="B60" s="160"/>
-      <c r="C60" s="160"/>
+      <c r="A60" s="150"/>
+      <c r="B60" s="150"/>
+      <c r="C60" s="150"/>
       <c r="D60" s="18">
         <v>7</v>
       </c>
@@ -9447,7 +9460,7 @@
       <c r="F60" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="G60" s="160"/>
+      <c r="G60" s="150"/>
       <c r="H60" s="21" t="s">
         <v>27</v>
       </c>
@@ -9485,13 +9498,13 @@
       <c r="J61" s="13"/>
     </row>
     <row r="62" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A62" s="144" t="s">
+      <c r="A62" s="139" t="s">
         <v>109</v>
       </c>
-      <c r="B62" s="144" t="s">
+      <c r="B62" s="139" t="s">
         <v>21</v>
       </c>
-      <c r="C62" s="144" t="s">
+      <c r="C62" s="139" t="s">
         <v>111</v>
       </c>
       <c r="D62" s="18">
@@ -9573,9 +9586,9 @@
       <c r="J65" s="13"/>
     </row>
     <row r="66" spans="1:10" ht="23.25" customHeight="1">
-      <c r="A66" s="160"/>
-      <c r="B66" s="160"/>
-      <c r="C66" s="160"/>
+      <c r="A66" s="150"/>
+      <c r="B66" s="150"/>
+      <c r="C66" s="150"/>
       <c r="D66" s="18">
         <v>7</v>
       </c>
@@ -9585,7 +9598,7 @@
       <c r="F66" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="G66" s="160"/>
+      <c r="G66" s="150"/>
       <c r="H66" s="21" t="s">
         <v>27</v>
       </c>
@@ -9623,13 +9636,13 @@
       <c r="J67" s="13"/>
     </row>
     <row r="68" spans="1:10" ht="18.75" customHeight="1">
-      <c r="A68" s="144" t="s">
+      <c r="A68" s="139" t="s">
         <v>115</v>
       </c>
-      <c r="B68" s="144" t="s">
+      <c r="B68" s="139" t="s">
         <v>21</v>
       </c>
-      <c r="C68" s="144" t="s">
+      <c r="C68" s="139" t="s">
         <v>116</v>
       </c>
       <c r="D68" s="18">
@@ -9711,9 +9724,9 @@
       <c r="J71" s="13"/>
     </row>
     <row r="72" spans="1:10" ht="21" customHeight="1">
-      <c r="A72" s="160"/>
-      <c r="B72" s="160"/>
-      <c r="C72" s="160"/>
+      <c r="A72" s="150"/>
+      <c r="B72" s="150"/>
+      <c r="C72" s="150"/>
       <c r="D72" s="18">
         <v>7</v>
       </c>
@@ -9723,7 +9736,7 @@
       <c r="F72" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="G72" s="160"/>
+      <c r="G72" s="150"/>
       <c r="H72" s="21" t="s">
         <v>27</v>
       </c>
@@ -9731,25 +9744,25 @@
       <c r="J72" s="13"/>
     </row>
     <row r="73" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A73" s="172"/>
-      <c r="B73" s="146"/>
-      <c r="C73" s="146"/>
-      <c r="D73" s="146"/>
-      <c r="E73" s="146"/>
-      <c r="F73" s="146"/>
-      <c r="G73" s="146"/>
-      <c r="H73" s="146"/>
+      <c r="A73" s="171"/>
+      <c r="B73" s="145"/>
+      <c r="C73" s="145"/>
+      <c r="D73" s="145"/>
+      <c r="E73" s="145"/>
+      <c r="F73" s="145"/>
+      <c r="G73" s="145"/>
+      <c r="H73" s="145"/>
       <c r="I73" s="170"/>
       <c r="J73" s="13"/>
     </row>
     <row r="74" spans="1:10" ht="18.75" customHeight="1">
-      <c r="A74" s="144" t="s">
+      <c r="A74" s="139" t="s">
         <v>115</v>
       </c>
-      <c r="B74" s="144" t="s">
+      <c r="B74" s="139" t="s">
         <v>57</v>
       </c>
-      <c r="C74" s="144" t="s">
+      <c r="C74" s="139" t="s">
         <v>120</v>
       </c>
       <c r="D74" s="18">
@@ -9831,9 +9844,9 @@
       <c r="J77" s="13"/>
     </row>
     <row r="78" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A78" s="160"/>
-      <c r="B78" s="160"/>
-      <c r="C78" s="160"/>
+      <c r="A78" s="150"/>
+      <c r="B78" s="150"/>
+      <c r="C78" s="150"/>
       <c r="D78" s="18">
         <v>7</v>
       </c>
@@ -9843,7 +9856,7 @@
       <c r="F78" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="G78" s="160"/>
+      <c r="G78" s="150"/>
       <c r="H78" s="21" t="s">
         <v>27</v>
       </c>
@@ -9851,25 +9864,25 @@
       <c r="J78" s="13"/>
     </row>
     <row r="79" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A79" s="172"/>
-      <c r="B79" s="146"/>
-      <c r="C79" s="146"/>
-      <c r="D79" s="146"/>
-      <c r="E79" s="146"/>
-      <c r="F79" s="146"/>
-      <c r="G79" s="146"/>
-      <c r="H79" s="146"/>
+      <c r="A79" s="171"/>
+      <c r="B79" s="145"/>
+      <c r="C79" s="145"/>
+      <c r="D79" s="145"/>
+      <c r="E79" s="145"/>
+      <c r="F79" s="145"/>
+      <c r="G79" s="145"/>
+      <c r="H79" s="145"/>
       <c r="I79" s="170"/>
       <c r="J79" s="13"/>
     </row>
     <row r="80" spans="1:10" ht="21.75" customHeight="1">
-      <c r="A80" s="144" t="s">
+      <c r="A80" s="139" t="s">
         <v>115</v>
       </c>
-      <c r="B80" s="144" t="s">
+      <c r="B80" s="139" t="s">
         <v>67</v>
       </c>
-      <c r="C80" s="144" t="s">
+      <c r="C80" s="139" t="s">
         <v>125</v>
       </c>
       <c r="D80" s="18">
@@ -9953,9 +9966,9 @@
       <c r="J83" s="13"/>
     </row>
     <row r="84" spans="1:10" ht="27" customHeight="1">
-      <c r="A84" s="160"/>
-      <c r="B84" s="160"/>
-      <c r="C84" s="160"/>
+      <c r="A84" s="150"/>
+      <c r="B84" s="150"/>
+      <c r="C84" s="150"/>
       <c r="D84" s="18">
         <v>7</v>
       </c>
@@ -9965,7 +9978,7 @@
       <c r="F84" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="G84" s="160"/>
+      <c r="G84" s="150"/>
       <c r="H84" s="21" t="s">
         <v>27</v>
       </c>
@@ -10003,13 +10016,13 @@
       <c r="J85" s="13"/>
     </row>
     <row r="86" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A86" s="144" t="s">
+      <c r="A86" s="139" t="s">
         <v>131</v>
       </c>
-      <c r="B86" s="144" t="s">
+      <c r="B86" s="139" t="s">
         <v>21</v>
       </c>
-      <c r="C86" s="144" t="s">
+      <c r="C86" s="139" t="s">
         <v>132</v>
       </c>
       <c r="D86" s="18">
@@ -10073,9 +10086,9 @@
       <c r="J88" s="13"/>
     </row>
     <row r="89" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A89" s="160"/>
-      <c r="B89" s="160"/>
-      <c r="C89" s="160"/>
+      <c r="A89" s="150"/>
+      <c r="B89" s="150"/>
+      <c r="C89" s="150"/>
       <c r="D89" s="18">
         <v>4</v>
       </c>
@@ -10085,7 +10098,7 @@
       <c r="F89" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="G89" s="160"/>
+      <c r="G89" s="150"/>
       <c r="H89" s="21" t="s">
         <v>27</v>
       </c>
@@ -10123,13 +10136,13 @@
       <c r="J90" s="13"/>
     </row>
     <row r="91" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A91" s="144" t="s">
+      <c r="A91" s="139" t="s">
         <v>143</v>
       </c>
-      <c r="B91" s="144" t="s">
+      <c r="B91" s="139" t="s">
         <v>21</v>
       </c>
-      <c r="C91" s="144" t="s">
+      <c r="C91" s="139" t="s">
         <v>145</v>
       </c>
       <c r="D91" s="18">
@@ -10213,9 +10226,9 @@
       <c r="J94" s="13"/>
     </row>
     <row r="95" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A95" s="160"/>
-      <c r="B95" s="160"/>
-      <c r="C95" s="160"/>
+      <c r="A95" s="150"/>
+      <c r="B95" s="150"/>
+      <c r="C95" s="150"/>
       <c r="D95" s="18">
         <v>10</v>
       </c>
@@ -10225,7 +10238,7 @@
       <c r="F95" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="G95" s="160"/>
+      <c r="G95" s="150"/>
       <c r="H95" s="21" t="s">
         <v>27</v>
       </c>
@@ -10263,13 +10276,13 @@
       <c r="J96" s="13"/>
     </row>
     <row r="97" spans="1:10" ht="25.5" customHeight="1">
-      <c r="A97" s="144" t="s">
+      <c r="A97" s="139" t="s">
         <v>150</v>
       </c>
-      <c r="B97" s="144" t="s">
+      <c r="B97" s="139" t="s">
         <v>21</v>
       </c>
-      <c r="C97" s="144" t="s">
+      <c r="C97" s="139" t="s">
         <v>151</v>
       </c>
       <c r="D97" s="18">
@@ -10331,9 +10344,9 @@
       <c r="J99" s="13"/>
     </row>
     <row r="100" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A100" s="160"/>
-      <c r="B100" s="160"/>
-      <c r="C100" s="160"/>
+      <c r="A100" s="150"/>
+      <c r="B100" s="150"/>
+      <c r="C100" s="150"/>
       <c r="D100" s="18">
         <v>4</v>
       </c>
@@ -10343,7 +10356,7 @@
       <c r="F100" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="G100" s="160"/>
+      <c r="G100" s="150"/>
       <c r="H100" s="21" t="s">
         <v>27</v>
       </c>
@@ -10381,13 +10394,13 @@
       <c r="J101" s="13"/>
     </row>
     <row r="102" spans="1:10" ht="38.25" customHeight="1">
-      <c r="A102" s="144" t="s">
+      <c r="A102" s="139" t="s">
         <v>157</v>
       </c>
-      <c r="B102" s="144" t="s">
+      <c r="B102" s="139" t="s">
         <v>21</v>
       </c>
-      <c r="C102" s="144" t="s">
+      <c r="C102" s="139" t="s">
         <v>158</v>
       </c>
       <c r="D102" s="18">
@@ -10409,9 +10422,9 @@
       <c r="J102" s="13"/>
     </row>
     <row r="103" spans="1:10" ht="44.25" customHeight="1">
-      <c r="A103" s="160"/>
-      <c r="B103" s="160"/>
-      <c r="C103" s="160"/>
+      <c r="A103" s="150"/>
+      <c r="B103" s="150"/>
+      <c r="C103" s="150"/>
       <c r="D103" s="18">
         <v>2</v>
       </c>
@@ -10421,7 +10434,7 @@
       <c r="F103" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="G103" s="160"/>
+      <c r="G103" s="150"/>
       <c r="H103" s="21" t="s">
         <v>27</v>
       </c>
@@ -10441,13 +10454,13 @@
       <c r="J104" s="13"/>
     </row>
     <row r="105" spans="1:10" ht="27" customHeight="1">
-      <c r="A105" s="144" t="s">
+      <c r="A105" s="139" t="s">
         <v>157</v>
       </c>
-      <c r="B105" s="144" t="s">
+      <c r="B105" s="139" t="s">
         <v>57</v>
       </c>
-      <c r="C105" s="144" t="s">
+      <c r="C105" s="139" t="s">
         <v>161</v>
       </c>
       <c r="D105" s="18">
@@ -10509,9 +10522,9 @@
       <c r="J107" s="13"/>
     </row>
     <row r="108" spans="1:10" ht="24.75" customHeight="1">
-      <c r="A108" s="160"/>
-      <c r="B108" s="160"/>
-      <c r="C108" s="160"/>
+      <c r="A108" s="150"/>
+      <c r="B108" s="150"/>
+      <c r="C108" s="150"/>
       <c r="D108" s="18">
         <v>4</v>
       </c>
@@ -10521,7 +10534,7 @@
       <c r="F108" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="G108" s="160"/>
+      <c r="G108" s="150"/>
       <c r="H108" s="21" t="s">
         <v>27</v>
       </c>
@@ -14100,76 +14113,6 @@
     </row>
   </sheetData>
   <mergeCells count="86">
-    <mergeCell ref="A44:A48"/>
-    <mergeCell ref="B44:B48"/>
-    <mergeCell ref="C44:C48"/>
-    <mergeCell ref="A49:I49"/>
-    <mergeCell ref="A50:A54"/>
-    <mergeCell ref="B50:B54"/>
-    <mergeCell ref="C50:C54"/>
-    <mergeCell ref="G50:G54"/>
-    <mergeCell ref="A55:I55"/>
-    <mergeCell ref="A56:A60"/>
-    <mergeCell ref="B56:B60"/>
-    <mergeCell ref="C56:C60"/>
-    <mergeCell ref="G56:G60"/>
-    <mergeCell ref="A62:A66"/>
-    <mergeCell ref="G62:G66"/>
-    <mergeCell ref="G74:G78"/>
-    <mergeCell ref="A79:I79"/>
-    <mergeCell ref="B62:B66"/>
-    <mergeCell ref="C62:C66"/>
-    <mergeCell ref="A68:A72"/>
-    <mergeCell ref="B68:B72"/>
-    <mergeCell ref="C68:C72"/>
-    <mergeCell ref="A73:I73"/>
-    <mergeCell ref="A74:A78"/>
-    <mergeCell ref="B74:B78"/>
-    <mergeCell ref="C74:C78"/>
-    <mergeCell ref="A80:A84"/>
-    <mergeCell ref="B80:B84"/>
-    <mergeCell ref="C80:C84"/>
-    <mergeCell ref="G80:G84"/>
-    <mergeCell ref="A86:A89"/>
-    <mergeCell ref="G86:G89"/>
-    <mergeCell ref="B86:B89"/>
-    <mergeCell ref="C86:C89"/>
-    <mergeCell ref="A105:A108"/>
-    <mergeCell ref="B105:B108"/>
-    <mergeCell ref="C105:C108"/>
-    <mergeCell ref="G97:G100"/>
-    <mergeCell ref="G102:G103"/>
-    <mergeCell ref="G105:G108"/>
-    <mergeCell ref="B97:B100"/>
-    <mergeCell ref="C97:C100"/>
-    <mergeCell ref="A102:A103"/>
-    <mergeCell ref="B102:B103"/>
-    <mergeCell ref="C102:C103"/>
-    <mergeCell ref="A91:A95"/>
-    <mergeCell ref="B91:B95"/>
-    <mergeCell ref="C91:C95"/>
-    <mergeCell ref="G91:G95"/>
-    <mergeCell ref="A97:A100"/>
-    <mergeCell ref="A2:A6"/>
-    <mergeCell ref="B2:B6"/>
-    <mergeCell ref="C2:C6"/>
-    <mergeCell ref="A7:I7"/>
-    <mergeCell ref="B8:B12"/>
-    <mergeCell ref="C8:C12"/>
-    <mergeCell ref="A26:A30"/>
-    <mergeCell ref="B26:B30"/>
-    <mergeCell ref="C26:C30"/>
-    <mergeCell ref="A31:I31"/>
-    <mergeCell ref="A8:A12"/>
-    <mergeCell ref="A14:A18"/>
-    <mergeCell ref="B14:B18"/>
-    <mergeCell ref="C14:C18"/>
-    <mergeCell ref="A20:A24"/>
-    <mergeCell ref="B20:B24"/>
-    <mergeCell ref="C20:C24"/>
-    <mergeCell ref="A19:I19"/>
-    <mergeCell ref="A25:I25"/>
-    <mergeCell ref="A13:I13"/>
     <mergeCell ref="A43:I43"/>
     <mergeCell ref="G44:G48"/>
     <mergeCell ref="G68:G72"/>
@@ -14186,6 +14129,76 @@
     <mergeCell ref="A38:A42"/>
     <mergeCell ref="B38:B42"/>
     <mergeCell ref="C38:C42"/>
+    <mergeCell ref="A26:A30"/>
+    <mergeCell ref="B26:B30"/>
+    <mergeCell ref="C26:C30"/>
+    <mergeCell ref="A31:I31"/>
+    <mergeCell ref="A8:A12"/>
+    <mergeCell ref="A14:A18"/>
+    <mergeCell ref="B14:B18"/>
+    <mergeCell ref="C14:C18"/>
+    <mergeCell ref="A20:A24"/>
+    <mergeCell ref="B20:B24"/>
+    <mergeCell ref="C20:C24"/>
+    <mergeCell ref="A19:I19"/>
+    <mergeCell ref="A25:I25"/>
+    <mergeCell ref="A13:I13"/>
+    <mergeCell ref="A2:A6"/>
+    <mergeCell ref="B2:B6"/>
+    <mergeCell ref="C2:C6"/>
+    <mergeCell ref="A7:I7"/>
+    <mergeCell ref="B8:B12"/>
+    <mergeCell ref="C8:C12"/>
+    <mergeCell ref="A91:A95"/>
+    <mergeCell ref="B91:B95"/>
+    <mergeCell ref="C91:C95"/>
+    <mergeCell ref="G91:G95"/>
+    <mergeCell ref="A97:A100"/>
+    <mergeCell ref="A105:A108"/>
+    <mergeCell ref="B105:B108"/>
+    <mergeCell ref="C105:C108"/>
+    <mergeCell ref="G97:G100"/>
+    <mergeCell ref="G102:G103"/>
+    <mergeCell ref="G105:G108"/>
+    <mergeCell ref="B97:B100"/>
+    <mergeCell ref="C97:C100"/>
+    <mergeCell ref="A102:A103"/>
+    <mergeCell ref="B102:B103"/>
+    <mergeCell ref="C102:C103"/>
+    <mergeCell ref="A80:A84"/>
+    <mergeCell ref="B80:B84"/>
+    <mergeCell ref="C80:C84"/>
+    <mergeCell ref="G80:G84"/>
+    <mergeCell ref="A86:A89"/>
+    <mergeCell ref="G86:G89"/>
+    <mergeCell ref="B86:B89"/>
+    <mergeCell ref="C86:C89"/>
+    <mergeCell ref="A62:A66"/>
+    <mergeCell ref="G62:G66"/>
+    <mergeCell ref="G74:G78"/>
+    <mergeCell ref="A79:I79"/>
+    <mergeCell ref="B62:B66"/>
+    <mergeCell ref="C62:C66"/>
+    <mergeCell ref="A68:A72"/>
+    <mergeCell ref="B68:B72"/>
+    <mergeCell ref="C68:C72"/>
+    <mergeCell ref="A73:I73"/>
+    <mergeCell ref="A74:A78"/>
+    <mergeCell ref="B74:B78"/>
+    <mergeCell ref="C74:C78"/>
+    <mergeCell ref="A55:I55"/>
+    <mergeCell ref="A56:A60"/>
+    <mergeCell ref="B56:B60"/>
+    <mergeCell ref="C56:C60"/>
+    <mergeCell ref="G56:G60"/>
+    <mergeCell ref="A44:A48"/>
+    <mergeCell ref="B44:B48"/>
+    <mergeCell ref="C44:C48"/>
+    <mergeCell ref="A49:I49"/>
+    <mergeCell ref="A50:A54"/>
+    <mergeCell ref="B50:B54"/>
+    <mergeCell ref="C50:C54"/>
+    <mergeCell ref="G50:G54"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -14193,20 +14206,20 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:AV1000"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.3984375" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" customWidth="1"/>
-    <col min="2" max="2" width="17.85546875" customWidth="1"/>
-    <col min="3" max="3" width="28.7109375" customWidth="1"/>
-    <col min="4" max="4" width="0.85546875" customWidth="1"/>
-    <col min="5" max="20" width="3.7109375" customWidth="1"/>
-    <col min="21" max="21" width="1.140625" customWidth="1"/>
-    <col min="22" max="48" width="3.7109375" customWidth="1"/>
+    <col min="1" max="1" width="2.73046875" customWidth="1"/>
+    <col min="2" max="2" width="17.86328125" customWidth="1"/>
+    <col min="3" max="3" width="28.73046875" customWidth="1"/>
+    <col min="4" max="4" width="0.86328125" customWidth="1"/>
+    <col min="5" max="20" width="3.73046875" customWidth="1"/>
+    <col min="21" max="21" width="1.1328125" customWidth="1"/>
+    <col min="22" max="48" width="3.73046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:48">
+    <row r="1" spans="1:48" ht="14.25">
       <c r="U1" s="2"/>
     </row>
     <row r="2" spans="1:48" ht="69.75" customHeight="1">
@@ -14214,7 +14227,7 @@
       <c r="B2" s="176" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="155"/>
+      <c r="C2" s="162"/>
       <c r="D2" s="8"/>
       <c r="E2" s="10">
         <v>41500</v>
@@ -14393,7 +14406,7 @@
       <c r="AT3" s="35"/>
       <c r="AU3" s="37"/>
     </row>
-    <row r="4" spans="1:48">
+    <row r="4" spans="1:48" ht="14.25">
       <c r="B4" s="177" t="s">
         <v>63</v>
       </c>
@@ -14445,7 +14458,7 @@
       <c r="AT4" s="40"/>
       <c r="AU4" s="44"/>
     </row>
-    <row r="5" spans="1:48">
+    <row r="5" spans="1:48" ht="14.25">
       <c r="B5" s="178"/>
       <c r="C5" s="47" t="s">
         <v>69</v>
@@ -14495,7 +14508,7 @@
       <c r="AT5" s="27"/>
       <c r="AU5" s="25"/>
     </row>
-    <row r="6" spans="1:48">
+    <row r="6" spans="1:48" ht="14.25">
       <c r="B6" s="178"/>
       <c r="C6" s="47" t="s">
         <v>76</v>
@@ -14545,7 +14558,7 @@
       <c r="AT6" s="27"/>
       <c r="AU6" s="25"/>
     </row>
-    <row r="7" spans="1:48">
+    <row r="7" spans="1:48" ht="14.25">
       <c r="B7" s="178"/>
       <c r="C7" s="47" t="s">
         <v>80</v>
@@ -14595,7 +14608,7 @@
       <c r="AT7" s="27"/>
       <c r="AU7" s="25"/>
     </row>
-    <row r="8" spans="1:48">
+    <row r="8" spans="1:48" ht="14.25">
       <c r="B8" s="178"/>
       <c r="C8" s="47" t="s">
         <v>83</v>
@@ -14645,7 +14658,7 @@
       <c r="AT8" s="27"/>
       <c r="AU8" s="25"/>
     </row>
-    <row r="9" spans="1:48">
+    <row r="9" spans="1:48" ht="14.25">
       <c r="B9" s="178"/>
       <c r="C9" s="47" t="s">
         <v>87</v>
@@ -14695,7 +14708,7 @@
       <c r="AT9" s="27"/>
       <c r="AU9" s="25"/>
     </row>
-    <row r="10" spans="1:48">
+    <row r="10" spans="1:48" ht="14.25">
       <c r="B10" s="178"/>
       <c r="C10" s="47" t="s">
         <v>90</v>
@@ -14745,7 +14758,7 @@
       <c r="AT10" s="27"/>
       <c r="AU10" s="25"/>
     </row>
-    <row r="11" spans="1:48">
+    <row r="11" spans="1:48" ht="14.25">
       <c r="B11" s="178"/>
       <c r="C11" s="47" t="s">
         <v>94</v>
@@ -14795,7 +14808,7 @@
       <c r="AT11" s="27"/>
       <c r="AU11" s="25"/>
     </row>
-    <row r="12" spans="1:48">
+    <row r="12" spans="1:48" ht="14.25">
       <c r="B12" s="178"/>
       <c r="C12" s="47" t="s">
         <v>96</v>
@@ -14845,7 +14858,7 @@
       <c r="AT12" s="27"/>
       <c r="AU12" s="25"/>
     </row>
-    <row r="13" spans="1:48">
+    <row r="13" spans="1:48" ht="14.25">
       <c r="B13" s="178"/>
       <c r="C13" s="47" t="s">
         <v>98</v>
@@ -14895,7 +14908,7 @@
       <c r="AT13" s="27"/>
       <c r="AU13" s="25"/>
     </row>
-    <row r="14" spans="1:48">
+    <row r="14" spans="1:48" ht="14.25">
       <c r="B14" s="178"/>
       <c r="C14" s="47" t="s">
         <v>100</v>
@@ -14945,7 +14958,7 @@
       <c r="AT14" s="27"/>
       <c r="AU14" s="25"/>
     </row>
-    <row r="15" spans="1:48">
+    <row r="15" spans="1:48" ht="14.25">
       <c r="B15" s="178"/>
       <c r="C15" s="47" t="s">
         <v>102</v>
@@ -14995,7 +15008,7 @@
       <c r="AT15" s="27"/>
       <c r="AU15" s="25"/>
     </row>
-    <row r="16" spans="1:48">
+    <row r="16" spans="1:48" ht="14.25">
       <c r="B16" s="178"/>
       <c r="C16" s="47" t="s">
         <v>104</v>
@@ -15045,7 +15058,7 @@
       <c r="AT16" s="27"/>
       <c r="AU16" s="25"/>
     </row>
-    <row r="17" spans="2:47">
+    <row r="17" spans="2:47" ht="14.25">
       <c r="B17" s="178"/>
       <c r="C17" s="47" t="s">
         <v>107</v>
@@ -15095,7 +15108,7 @@
       <c r="AT17" s="27"/>
       <c r="AU17" s="25"/>
     </row>
-    <row r="18" spans="2:47">
+    <row r="18" spans="2:47" ht="14.25">
       <c r="B18" s="179"/>
       <c r="C18" s="67" t="s">
         <v>110</v>
@@ -15145,7 +15158,7 @@
       <c r="AT18" s="27"/>
       <c r="AU18" s="25"/>
     </row>
-    <row r="19" spans="2:47">
+    <row r="19" spans="2:47" ht="14.25">
       <c r="B19" s="177" t="s">
         <v>113</v>
       </c>
@@ -15197,7 +15210,7 @@
       <c r="AT19" s="27"/>
       <c r="AU19" s="25"/>
     </row>
-    <row r="20" spans="2:47">
+    <row r="20" spans="2:47" ht="14.25">
       <c r="B20" s="178"/>
       <c r="C20" s="47" t="s">
         <v>117</v>
@@ -20013,32 +20026,32 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:Z1000"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.3984375" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="3.140625" customWidth="1"/>
-    <col min="2" max="2" width="17.85546875" customWidth="1"/>
-    <col min="3" max="3" width="28.7109375" customWidth="1"/>
-    <col min="4" max="4" width="0.85546875" customWidth="1"/>
-    <col min="5" max="5" width="13.85546875" customWidth="1"/>
-    <col min="6" max="6" width="3.28515625" customWidth="1"/>
-    <col min="7" max="20" width="3.7109375" customWidth="1"/>
-    <col min="21" max="21" width="1.140625" customWidth="1"/>
-    <col min="22" max="25" width="3.7109375" customWidth="1"/>
-    <col min="26" max="26" width="10.7109375" customWidth="1"/>
+    <col min="1" max="1" width="3.1328125" customWidth="1"/>
+    <col min="2" max="2" width="17.86328125" customWidth="1"/>
+    <col min="3" max="3" width="28.73046875" customWidth="1"/>
+    <col min="4" max="4" width="0.86328125" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" customWidth="1"/>
+    <col min="6" max="6" width="3.265625" customWidth="1"/>
+    <col min="7" max="20" width="3.73046875" customWidth="1"/>
+    <col min="21" max="21" width="1.1328125" customWidth="1"/>
+    <col min="22" max="25" width="3.73046875" customWidth="1"/>
+    <col min="26" max="26" width="10.73046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26">
+    <row r="1" spans="1:26" ht="14.25">
       <c r="E1" s="58"/>
       <c r="U1" s="2"/>
     </row>
-    <row r="2" spans="1:26">
+    <row r="2" spans="1:26" ht="14.25">
       <c r="A2" s="4"/>
       <c r="B2" s="176" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="155"/>
+      <c r="C2" s="162"/>
       <c r="D2" s="8"/>
       <c r="E2" s="59" t="s">
         <v>92</v>
@@ -20091,7 +20104,7 @@
       <c r="X3" s="2"/>
       <c r="Y3" s="2"/>
     </row>
-    <row r="4" spans="1:26">
+    <row r="4" spans="1:26" ht="14.25">
       <c r="B4" s="177" t="s">
         <v>63</v>
       </c>
@@ -20123,7 +20136,7 @@
       <c r="X4" s="2"/>
       <c r="Y4" s="2"/>
     </row>
-    <row r="5" spans="1:26">
+    <row r="5" spans="1:26" ht="14.25">
       <c r="B5" s="178"/>
       <c r="C5" s="47" t="s">
         <v>69</v>
@@ -20151,7 +20164,7 @@
       <c r="X5" s="2"/>
       <c r="Y5" s="2"/>
     </row>
-    <row r="6" spans="1:26">
+    <row r="6" spans="1:26" ht="14.25">
       <c r="B6" s="178"/>
       <c r="C6" s="47" t="s">
         <v>76</v>
@@ -20179,7 +20192,7 @@
       <c r="X6" s="2"/>
       <c r="Y6" s="2"/>
     </row>
-    <row r="7" spans="1:26">
+    <row r="7" spans="1:26" ht="14.25">
       <c r="B7" s="178"/>
       <c r="C7" s="47" t="s">
         <v>80</v>
@@ -20207,7 +20220,7 @@
       <c r="X7" s="2"/>
       <c r="Y7" s="2"/>
     </row>
-    <row r="8" spans="1:26">
+    <row r="8" spans="1:26" ht="14.25">
       <c r="B8" s="178"/>
       <c r="C8" s="47" t="s">
         <v>83</v>
@@ -20235,7 +20248,7 @@
       <c r="X8" s="2"/>
       <c r="Y8" s="2"/>
     </row>
-    <row r="9" spans="1:26">
+    <row r="9" spans="1:26" ht="14.25">
       <c r="B9" s="178"/>
       <c r="C9" s="47" t="s">
         <v>87</v>
@@ -20265,7 +20278,7 @@
       <c r="X9" s="2"/>
       <c r="Y9" s="2"/>
     </row>
-    <row r="10" spans="1:26">
+    <row r="10" spans="1:26" ht="14.25">
       <c r="B10" s="178"/>
       <c r="C10" s="47" t="s">
         <v>90</v>
@@ -20293,7 +20306,7 @@
       <c r="X10" s="2"/>
       <c r="Y10" s="2"/>
     </row>
-    <row r="11" spans="1:26">
+    <row r="11" spans="1:26" ht="14.25">
       <c r="B11" s="178"/>
       <c r="C11" s="47" t="s">
         <v>94</v>
@@ -20321,7 +20334,7 @@
       <c r="X11" s="2"/>
       <c r="Y11" s="2"/>
     </row>
-    <row r="12" spans="1:26">
+    <row r="12" spans="1:26" ht="14.25">
       <c r="B12" s="178"/>
       <c r="C12" s="47" t="s">
         <v>96</v>
@@ -20349,7 +20362,7 @@
       <c r="X12" s="2"/>
       <c r="Y12" s="2"/>
     </row>
-    <row r="13" spans="1:26">
+    <row r="13" spans="1:26" ht="14.25">
       <c r="B13" s="178"/>
       <c r="C13" s="47" t="s">
         <v>98</v>
@@ -20377,7 +20390,7 @@
       <c r="X13" s="2"/>
       <c r="Y13" s="2"/>
     </row>
-    <row r="14" spans="1:26">
+    <row r="14" spans="1:26" ht="14.25">
       <c r="B14" s="178"/>
       <c r="C14" s="47" t="s">
         <v>100</v>
@@ -20405,7 +20418,7 @@
       <c r="X14" s="2"/>
       <c r="Y14" s="2"/>
     </row>
-    <row r="15" spans="1:26">
+    <row r="15" spans="1:26" ht="14.25">
       <c r="B15" s="178"/>
       <c r="C15" s="47" t="s">
         <v>102</v>
@@ -20433,7 +20446,7 @@
       <c r="X15" s="2"/>
       <c r="Y15" s="2"/>
     </row>
-    <row r="16" spans="1:26">
+    <row r="16" spans="1:26" ht="14.25">
       <c r="B16" s="178"/>
       <c r="C16" s="47" t="s">
         <v>104</v>
@@ -20461,7 +20474,7 @@
       <c r="X16" s="2"/>
       <c r="Y16" s="2"/>
     </row>
-    <row r="17" spans="2:25">
+    <row r="17" spans="2:25" ht="14.25">
       <c r="B17" s="178"/>
       <c r="C17" s="47" t="s">
         <v>107</v>
@@ -20491,7 +20504,7 @@
       <c r="X17" s="2"/>
       <c r="Y17" s="2"/>
     </row>
-    <row r="18" spans="2:25">
+    <row r="18" spans="2:25" ht="14.25">
       <c r="B18" s="179"/>
       <c r="C18" s="67" t="s">
         <v>110</v>
@@ -20519,7 +20532,7 @@
       <c r="X18" s="2"/>
       <c r="Y18" s="2"/>
     </row>
-    <row r="19" spans="2:25">
+    <row r="19" spans="2:25" ht="14.25">
       <c r="B19" s="177" t="s">
         <v>113</v>
       </c>
@@ -20551,7 +20564,7 @@
       <c r="X19" s="2"/>
       <c r="Y19" s="2"/>
     </row>
-    <row r="20" spans="2:25">
+    <row r="20" spans="2:25" ht="14.25">
       <c r="B20" s="178"/>
       <c r="C20" s="47" t="s">
         <v>117</v>
